--- a/青山市实验高中贫困生补助名单.xlsx
+++ b/青山市实验高中贫困生补助名单.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25043F9E-4BA8-CA49-BB7D-5CBA9C2D5BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jhk66\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236E5D40-35FA-4A86-922E-9920F03EEBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1700" yWindow="2690" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="贫困生补助名单" sheetId="1" r:id="rId1"/>
@@ -27,8 +32,29 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={92DFD4CF-ED45-4F83-8F51-562C11E317A5}</author>
+  </authors>
+  <commentList>
+    <comment ref="G6" authorId="0" shapeId="0" xr:uid="{92DFD4CF-ED45-4F83-8F51-562C11E317A5}">
+      <text>
+        <t>[线程批注]
+你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
+注释:
+    2026.09.24
+补充材料已整理完毕，暂存于青山市实验中学教务处档案柜。
+访问方式：qssgaj.pages.dev/evidence.html
+—— 张乔晞</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="49">
   <si>
     <t>青山市实验高中 2026-2027 学年度贫困生补助名单</t>
   </si>
@@ -169,13 +195,77 @@
   </si>
   <si>
     <t>共7人</t>
+  </si>
+  <si>
+    <t>附注</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>本表与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2026.09.24 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>补充材料一并归档。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="0"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>qssgaj.pages.dev/evidence.html</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  —— </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>张乔晞</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,38 +277,98 @@
       <b/>
       <sz val="16"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <strike/>
       <sz val="11"/>
       <color rgb="FF999999"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="0"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="0" tint="-0.34998626667073579"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -268,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -317,6 +467,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -332,6 +485,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="洪坤 计" id="{8FCF36B1-59B8-4D05-8B05-31682ECBAA69}" userId="53b425202489e5df" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -617,20 +776,31 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="G6" dT="2026-10-04T07:44:24.12" personId="{8FCF36B1-59B8-4D05-8B05-31682ECBAA69}" id="{92DFD4CF-ED45-4F83-8F51-562C11E317A5}">
+    <text>2026.09.24
+补充材料已整理完毕，暂存于青山市实验中学教务处档案柜。
+访问方式：qssgaj.pages.dev/evidence.html
+—— 张乔晞</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.99609375" customWidth="1"/>
-    <col min="2" max="3" width="9.953125" customWidth="1"/>
-    <col min="4" max="4" width="14.04296875" customWidth="1"/>
-    <col min="5" max="5" width="11.99609375" customWidth="1"/>
-    <col min="6" max="6" width="14.04296875" customWidth="1"/>
-    <col min="7" max="7" width="17.99609375" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="3" width="9.90625" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -641,7 +811,7 @@
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
     </row>
-    <row r="2" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="2" spans="1:7" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>45</v>
       </c>
@@ -652,7 +822,7 @@
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
     </row>
-    <row r="3" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -675,7 +845,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="4" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -698,7 +868,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -721,7 +891,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -744,7 +914,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -767,7 +937,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="8" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -790,7 +960,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="9" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -813,7 +983,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="10" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -836,7 +1006,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="11" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -859,7 +1029,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.1">
+    <row r="12" spans="1:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>38</v>
       </c>
@@ -874,7 +1044,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.1">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>39</v>
       </c>
@@ -885,7 +1055,7 @@
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.1">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>42</v>
       </c>
@@ -900,7 +1070,17 @@
       </c>
       <c r="G16" s="12"/>
     </row>
-    <row r="17" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.1"/>
+    <row r="17" spans="1:7" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G18" s="20"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A14:G14"/>
@@ -911,7 +1091,9 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A16:C16"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.6" right="0.6" top="0.8" bottom="0.8" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>